--- a/docs/05_records/08_AI_오류_기록_VBC_v1.0.xlsx
+++ b/docs/05_records/08_AI_오류_기록_VBC_v1.0.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -989,6 +989,51 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>문서</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>README 최종본 작성</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>'C1~C5, L1~L6'처럼 '~'를 두 번 쓰면 GitHub에서 그 사이가 취소선으로 보이는 문제를 고려하지 않음</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>팀장이 GitHub 화면에서 취소선을 발견</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>코드 밖의 '~'를 '\~'로 바꾸고 GitHub 마크다운 변환 API로 취소선 0개 확인 (README, web/README, CLAUDE.md)</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>README.md, PR #16</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>파일 내용뿐 아니라 실제 보이는 화면까지 확인</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
